--- a/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007</t>
+          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>81876</t>
+          <t>80843</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119790</t>
+          <t>119793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>170845</t>
+          <t>171622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>221745</t>
+          <t>222974</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>265234</t>
+          <t>264376</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329304</t>
+          <t>330038</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>911933</t>
+          <t>911930</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>949847</t>
+          <t>950880</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1093368</t>
+          <t>1092139</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1144268</t>
+          <t>1143491</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2017531</t>
+          <t>2016797</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2081601</t>
+          <t>2082459</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72765</t>
+          <t>75692</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112744</t>
+          <t>114554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46937</t>
+          <t>48553</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80236</t>
+          <t>80328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>130583</t>
+          <t>133343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180047</t>
+          <t>183335</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1580669</t>
+          <t>1578859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1620648</t>
+          <t>1617721</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1507437</t>
+          <t>1507345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1540736</t>
+          <t>1539120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3101039</t>
+          <t>3097751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3150503</t>
+          <t>3147743</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,94%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33829</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62039</t>
+          <t>63527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27230</t>
+          <t>27248</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48934</t>
+          <t>49269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68560</t>
+          <t>68732</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>103290</t>
+          <t>102863</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,01%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>489369</t>
+          <t>487881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517579</t>
+          <t>516955</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>427478</t>
+          <t>427143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449182</t>
+          <t>449164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924530</t>
+          <t>924957</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>959260</t>
+          <t>959088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,31%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>209536</t>
+          <t>208080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>267820</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>263461</t>
+          <t>264324</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>331569</t>
+          <t>329422</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>489298</t>
+          <t>494099</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>577801</t>
+          <t>579992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3008723</t>
+          <t>3008422</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3067007</t>
+          <t>3068463</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3047628</t>
+          <t>3049775</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3115736</t>
+          <t>3114873</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6077940</t>
+          <t>6075749</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6166443</t>
+          <t>6161642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012</t>
+          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85229</t>
+          <t>86169</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123868</t>
+          <t>124883</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>188811</t>
+          <t>192179</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>246376</t>
+          <t>247293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291270</t>
+          <t>291959</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>360100</t>
+          <t>361052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,61%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>850775</t>
+          <t>849760</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>889414</t>
+          <t>888474</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1091421</t>
+          <t>1090504</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1148986</t>
+          <t>1145618</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1952340</t>
+          <t>1951388</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2021170</t>
+          <t>2020481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,37%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>99631</t>
+          <t>100313</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143233</t>
+          <t>147586</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64450</t>
+          <t>65439</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102334</t>
+          <t>101099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172446</t>
+          <t>174751</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232819</t>
+          <t>233979</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1820724</t>
+          <t>1816371</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1864326</t>
+          <t>1863644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1655469</t>
+          <t>1656704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1693353</t>
+          <t>1692364</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3488941</t>
+          <t>3487781</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3549314</t>
+          <t>3547009</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45181</t>
+          <t>45257</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75034</t>
+          <t>74783</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38265</t>
+          <t>38162</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65734</t>
+          <t>66347</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89534</t>
+          <t>89669</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129486</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406147</t>
+          <t>406398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>436000</t>
+          <t>435924</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392897</t>
+          <t>392284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>420366</t>
+          <t>420469</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>810327</t>
+          <t>809084</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>850279</t>
+          <t>850144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>246690</t>
+          <t>248647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>319112</t>
+          <t>317183</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>312352</t>
+          <t>313274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>389335</t>
+          <t>387021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>585563</t>
+          <t>584901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>686457</t>
+          <t>683835</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3100670</t>
+          <t>3102599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3173092</t>
+          <t>3171135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3164895</t>
+          <t>3167209</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3241878</t>
+          <t>3240956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6287555</t>
+          <t>6290177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6388449</t>
+          <t>6389111</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016</t>
+          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108263</t>
+          <t>106579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>147228</t>
+          <t>148173</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>178453</t>
+          <t>177239</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>227972</t>
+          <t>228622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>294340</t>
+          <t>295496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>363328</t>
+          <t>363218</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>607119</t>
+          <t>606174</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>646084</t>
+          <t>647768</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>766688</t>
+          <t>766038</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>816207</t>
+          <t>817421</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1385679</t>
+          <t>1385789</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1454667</t>
+          <t>1453511</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175498</t>
+          <t>175853</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>229931</t>
+          <t>233760</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165798</t>
+          <t>167559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221159</t>
+          <t>220862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>356531</t>
+          <t>359376</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>430571</t>
+          <t>435993</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1846454</t>
+          <t>1842625</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1900887</t>
+          <t>1900532</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1767141</t>
+          <t>1767438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1822502</t>
+          <t>1820741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3634114</t>
+          <t>3628692</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3708154</t>
+          <t>3705309</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,16%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>78768</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117126</t>
+          <t>117467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54984</t>
+          <t>55960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88328</t>
+          <t>89003</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>141131</t>
+          <t>143371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193003</t>
+          <t>194890</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429760</t>
+          <t>429419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>468118</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460812</t>
+          <t>460137</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>494156</t>
+          <t>493180</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>903024</t>
+          <t>901137</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>954896</t>
+          <t>952656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,92%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>389902</t>
+          <t>386298</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>468247</t>
+          <t>463286</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>426949</t>
+          <t>424503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>510664</t>
+          <t>507225</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>833335</t>
+          <t>837130</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>948919</t>
+          <t>948290</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,72%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2909371</t>
+          <t>2914332</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2987716</t>
+          <t>2991320</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3021436</t>
+          <t>3024875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3105151</t>
+          <t>3107597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5960799</t>
+          <t>5961428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6076383</t>
+          <t>6072588</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,88%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023</t>
+          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124391</t>
+          <t>123704</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>160490</t>
+          <t>161446</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>249057</t>
+          <t>246479</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288172</t>
+          <t>288730</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>383655</t>
+          <t>381668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>437805</t>
+          <t>435620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>34,29%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354448</t>
+          <t>353492</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>390547</t>
+          <t>391234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>467336</t>
+          <t>466778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>506451</t>
+          <t>509029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>832641</t>
+          <t>834826</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>886791</t>
+          <t>888778</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,96%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230016</t>
+          <t>225393</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>392626</t>
+          <t>395498</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173501</t>
+          <t>168076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>268956</t>
+          <t>272118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>458422</t>
+          <t>456498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644072</t>
+          <t>644643</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1897701</t>
+          <t>1894829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2060311</t>
+          <t>2064934</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1968867</t>
+          <t>1965705</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2064322</t>
+          <t>2069747</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3884078</t>
+          <t>3883507</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4069728</t>
+          <t>4071652</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80391</t>
+          <t>80307</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>119229</t>
+          <t>115854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85374</t>
+          <t>85422</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114248</t>
+          <t>117042</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172237</t>
+          <t>174947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220858</t>
+          <t>224523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>527394</t>
+          <t>530769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566232</t>
+          <t>566316</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>546215</t>
+          <t>543421</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575089</t>
+          <t>575041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1086228</t>
+          <t>1082563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1134849</t>
+          <t>1132139</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>449658</t>
+          <t>450238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>641760</t>
+          <t>639860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>492241</t>
+          <t>489164</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>656244</t>
+          <t>654299</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1028205</t>
+          <t>1019083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1272746</t>
+          <t>1266190</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2810129</t>
+          <t>2812029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3002231</t>
+          <t>3001651</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2997550</t>
+          <t>2999495</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3161553</t>
+          <t>3164630</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5832937</t>
+          <t>5839493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6077478</t>
+          <t>6086600</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80843</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119793</t>
+          <t>120038</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>171622</t>
+          <t>171139</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>222974</t>
+          <t>222696</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264376</t>
+          <t>263996</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>330038</t>
+          <t>331567</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>911930</t>
+          <t>911685</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>950880</t>
+          <t>951074</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1092139</t>
+          <t>1092417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1143491</t>
+          <t>1143974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2016797</t>
+          <t>2015268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2082459</t>
+          <t>2082839</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,75%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75692</t>
+          <t>74744</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>114554</t>
+          <t>114346</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48553</t>
+          <t>48872</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80328</t>
+          <t>82709</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>133343</t>
+          <t>131952</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>183335</t>
+          <t>181504</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1578859</t>
+          <t>1579067</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1617721</t>
+          <t>1618669</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1507345</t>
+          <t>1504964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1539120</t>
+          <t>1538801</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3097751</t>
+          <t>3099582</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3147743</t>
+          <t>3149134</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>35862</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63527</t>
+          <t>62913</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27248</t>
+          <t>26200</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49269</t>
+          <t>49223</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68732</t>
+          <t>67900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102863</t>
+          <t>102201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>487881</t>
+          <t>488495</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>516955</t>
+          <t>515546</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>427143</t>
+          <t>427189</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>449164</t>
+          <t>450212</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924957</t>
+          <t>925619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>959088</t>
+          <t>959920</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>208080</t>
+          <t>209412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>268121</t>
+          <t>271884</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>264324</t>
+          <t>261588</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>329422</t>
+          <t>329584</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>494099</t>
+          <t>489979</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>579992</t>
+          <t>582606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3008422</t>
+          <t>3004659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3068463</t>
+          <t>3067131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3049775</t>
+          <t>3049613</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3114873</t>
+          <t>3117609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6075749</t>
+          <t>6073135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6161642</t>
+          <t>6165762</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,64%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86169</t>
+          <t>85603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>124883</t>
+          <t>127375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192179</t>
+          <t>192973</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>247293</t>
+          <t>247506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>291959</t>
+          <t>288235</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>361052</t>
+          <t>360174</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>849760</t>
+          <t>847268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>888474</t>
+          <t>889040</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1090504</t>
+          <t>1090291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1145618</t>
+          <t>1144824</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1951388</t>
+          <t>1952266</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2020481</t>
+          <t>2024205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,39%</t>
+          <t>84,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100313</t>
+          <t>100532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147586</t>
+          <t>146323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65439</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101099</t>
+          <t>103078</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>174751</t>
+          <t>174430</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>233979</t>
+          <t>233308</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1816371</t>
+          <t>1817634</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1863644</t>
+          <t>1863425</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1656704</t>
+          <t>1654725</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1692364</t>
+          <t>1693982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3487781</t>
+          <t>3488452</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3547009</t>
+          <t>3547330</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>45257</t>
+          <t>43666</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74783</t>
+          <t>76849</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38162</t>
+          <t>37319</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66347</t>
+          <t>65740</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89669</t>
+          <t>89512</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130729</t>
+          <t>132528</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,1%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>406398</t>
+          <t>404332</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>435924</t>
+          <t>437515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>392284</t>
+          <t>392891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>420469</t>
+          <t>421312</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>809084</t>
+          <t>807285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>850144</t>
+          <t>850301</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>90,48%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>248647</t>
+          <t>251230</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>317183</t>
+          <t>319401</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>313274</t>
+          <t>314678</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>387021</t>
+          <t>388887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>584901</t>
+          <t>581328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>683835</t>
+          <t>687337</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3102599</t>
+          <t>3100381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3171135</t>
+          <t>3168552</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3167209</t>
+          <t>3165343</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3240956</t>
+          <t>3239552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6290177</t>
+          <t>6286675</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6389111</t>
+          <t>6392684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>106579</t>
+          <t>106738</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>148173</t>
+          <t>145693</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>177239</t>
+          <t>175362</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228622</t>
+          <t>230398</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>295496</t>
+          <t>297583</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>363218</t>
+          <t>366084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>606174</t>
+          <t>608654</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>647768</t>
+          <t>647609</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>766038</t>
+          <t>764262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>817421</t>
+          <t>819298</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>76,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1385789</t>
+          <t>1382923</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1453511</t>
+          <t>1451424</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,23%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175853</t>
+          <t>172379</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233760</t>
+          <t>226837</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>167559</t>
+          <t>170559</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>220862</t>
+          <t>225777</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>359376</t>
+          <t>355061</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>435993</t>
+          <t>431008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1842625</t>
+          <t>1849548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1900532</t>
+          <t>1904006</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1767438</t>
+          <t>1762523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1820741</t>
+          <t>1817741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3628692</t>
+          <t>3633677</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3705309</t>
+          <t>3709624</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,26%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78768</t>
+          <t>79064</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>117467</t>
+          <t>117386</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55960</t>
+          <t>55599</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89003</t>
+          <t>88424</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143371</t>
+          <t>144291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>194890</t>
+          <t>193022</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>429419</t>
+          <t>429500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>468118</t>
+          <t>467822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>460137</t>
+          <t>460716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493180</t>
+          <t>493541</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>901137</t>
+          <t>903005</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>952656</t>
+          <t>951736</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>86,84%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>386298</t>
+          <t>388326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>463286</t>
+          <t>468811</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>424503</t>
+          <t>423660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>507225</t>
+          <t>506910</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>837130</t>
+          <t>833542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>948290</t>
+          <t>946142</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,69%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2914332</t>
+          <t>2908807</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2991320</t>
+          <t>2989292</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3024875</t>
+          <t>3025190</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3107597</t>
+          <t>3108440</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5961428</t>
+          <t>5963576</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6072588</t>
+          <t>6076176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>141064</t>
+          <t>163184</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123704</t>
+          <t>141604</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>161446</t>
+          <t>185030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>267797</t>
+          <t>286308</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>246479</t>
+          <t>266116</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>288730</t>
+          <t>308352</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>408861</t>
+          <t>449492</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>381668</t>
+          <t>421330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>435620</t>
+          <t>480367</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,29%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>373874</t>
+          <t>415345</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>353492</t>
+          <t>393499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>391234</t>
+          <t>436925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,61%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>487711</t>
+          <t>535730</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>466778</t>
+          <t>513686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>509029</t>
+          <t>555922</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,78%</t>
+          <t>62,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>861585</t>
+          <t>951075</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>834826</t>
+          <t>920200</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>888778</t>
+          <t>979237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,71%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>338199</t>
+          <t>374581</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225393</t>
+          <t>339942</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>395498</t>
+          <t>414758</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>232189</t>
+          <t>258961</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168076</t>
+          <t>235207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>286282</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>570388</t>
+          <t>633542</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>456498</t>
+          <t>589179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644643</t>
+          <t>679231</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>15,43%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1952128</t>
+          <t>1855985</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1894829</t>
+          <t>1815808</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2064934</t>
+          <t>1890624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2005634</t>
+          <t>1912431</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1965705</t>
+          <t>1885110</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2069747</t>
+          <t>1936185</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3957762</t>
+          <t>3768417</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3883507</t>
+          <t>3722728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4071652</t>
+          <t>3812780</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>96699</t>
+          <t>109545</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80307</t>
+          <t>91507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>115854</t>
+          <t>130136</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99838</t>
+          <t>109443</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>85422</t>
+          <t>93054</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117042</t>
+          <t>127174</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>196537</t>
+          <t>218987</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174947</t>
+          <t>194395</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>224523</t>
+          <t>247257</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>549924</t>
+          <t>602042</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>530769</t>
+          <t>581451</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>566316</t>
+          <t>620080</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>560625</t>
+          <t>625434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>543421</t>
+          <t>607703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>575041</t>
+          <t>641823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1110549</t>
+          <t>1227477</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1082563</t>
+          <t>1199207</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1132139</t>
+          <t>1252069</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,56%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>575962</t>
+          <t>647310</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>450238</t>
+          <t>602917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>639860</t>
+          <t>698325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>599825</t>
+          <t>654711</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>489164</t>
+          <t>617679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>654299</t>
+          <t>694076</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1175786</t>
+          <t>1302021</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1019083</t>
+          <t>1235685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1266190</t>
+          <t>1364671</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2875927</t>
+          <t>2873373</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2812029</t>
+          <t>2822358</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3001651</t>
+          <t>2917766</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,17%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3053969</t>
+          <t>3073596</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2999495</t>
+          <t>3034231</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3164630</t>
+          <t>3110628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>82,44%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5929897</t>
+          <t>5946969</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5839493</t>
+          <t>5884319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6086600</t>
+          <t>6013305</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares unipersonales en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si conforma un hogar unipersonal en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
